--- a/data/trans_bre/P16A15-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A15-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,86</t>
+          <t>1,3; 6,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 6,75</t>
+          <t>-0,21; 6,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 7,9</t>
+          <t>-0,21; 7,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 10,78</t>
+          <t>2,88; 10,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,16; 68,02</t>
+          <t>10,05; 69,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 35,91</t>
+          <t>-0,88; 37,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 43,05</t>
+          <t>-1,22; 39,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 50,12</t>
+          <t>10,57; 49,94</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,48</t>
+          <t>-1,08; 1,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,91</t>
+          <t>-2,3; 1,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,36</t>
+          <t>-1,5; 1,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 31,8</t>
+          <t>-1,19; 31,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 55,87</t>
+          <t>-29,01; 52,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 18,5</t>
+          <t>-33,53; 19,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 23,59</t>
+          <t>-21,34; 28,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 357,24</t>
+          <t>-12,19; 339,55</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,91</t>
+          <t>-3,32; 0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; -0,23</t>
+          <t>-6,33; 0,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,36</t>
+          <t>-4,35; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,65</t>
+          <t>-2,77; 2,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-69,54; 38,9</t>
+          <t>-67,54; 40,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,11; 2,56</t>
+          <t>-72,73; 7,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,48; 20,07</t>
+          <t>-71,55; 25,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 34,52</t>
+          <t>-26,56; 34,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,38</t>
+          <t>0,83; 3,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,55</t>
+          <t>0,5; 3,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,07</t>
+          <t>0,23; 3,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 21,59</t>
+          <t>1,57; 22,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,64; 63,22</t>
+          <t>13,13; 61,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 38,0</t>
+          <t>4,21; 38,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 34,73</t>
+          <t>2,29; 37,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 206,69</t>
+          <t>12,55; 214,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A15-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A15-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,71</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,73</t>
+          <t>1,46; 6,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 6,93</t>
+          <t>-0,14; 7,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 7,66</t>
+          <t>0,18; 8,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,63</t>
+          <t>4,59; 12,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,05; 69,17</t>
+          <t>10,86; 69,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 37,33</t>
+          <t>-0,77; 38,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 39,81</t>
+          <t>0,7; 42,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 49,94</t>
+          <t>17,68; 61,31</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>-11,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,45</t>
+          <t>-0,99; 1,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,04</t>
+          <t>-2,2; 1,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,56</t>
+          <t>-1,64; 1,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 31,16</t>
+          <t>-2,62; 0,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 52,53</t>
+          <t>-27,63; 56,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,53; 19,42</t>
+          <t>-32,67; 21,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 28,17</t>
+          <t>-22,6; 26,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 339,55</t>
+          <t>-23,45; 4,35</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,8</t>
+          <t>-3,33; 0,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 0,14</t>
+          <t>-6,65; 0,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 0,87</t>
+          <t>-4,43; 0,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,62</t>
+          <t>-2,38; 2,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,54; 40,52</t>
+          <t>-69,05; 36,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 7,87</t>
+          <t>-74,05; 4,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-71,55; 25,08</t>
+          <t>-71,99; 25,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 34,87</t>
+          <t>-22,9; 36,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,24</t>
+          <t>0,86; 3,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,76</t>
+          <t>0,29; 3,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,16</t>
+          <t>0,14; 3,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 22,87</t>
+          <t>0,5; 3,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 61,62</t>
+          <t>13,46; 62,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 38,3</t>
+          <t>2,72; 36,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 37,45</t>
+          <t>1,4; 35,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 214,07</t>
+          <t>3,86; 28,6</t>
         </is>
       </c>
     </row>
